--- a/pipeline/TOFU_16S/Kraken/script/output/ML_results.xlsx
+++ b/pipeline/TOFU_16S/Kraken/script/output/ML_results.xlsx
@@ -395,19 +395,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.696428571428571</v>
+        <v>0.708333333333333</v>
       </c>
       <c r="B2" t="n">
-        <v>0.742925824175824</v>
+        <v>0.763560744810745</v>
       </c>
       <c r="C2" t="n">
-        <v>0.916666666666667</v>
+        <v>0.927083333333333</v>
       </c>
       <c r="D2" t="n">
         <v>0.75</v>
       </c>
       <c r="E2" t="n">
-        <v>0.664626528442318</v>
+        <v>0.67721394102973</v>
       </c>
       <c r="F2" t="s">
         <v>6</v>
@@ -435,19 +435,19 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.688775510204082</v>
+        <v>0.647959183673469</v>
       </c>
       <c r="B4" t="n">
-        <v>0.708917867846439</v>
+        <v>0.681392615321187</v>
       </c>
       <c r="C4" t="n">
-        <v>0.895833333333333</v>
+        <v>0.8125</v>
       </c>
       <c r="D4" t="n">
-        <v>0.761904761904762</v>
+        <v>0.714285714285714</v>
       </c>
       <c r="E4" t="n">
-        <v>0.660759390248554</v>
+        <v>0.625967140015128</v>
       </c>
       <c r="F4" t="s">
         <v>8</v>
@@ -455,19 +455,19 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.709183673469388</v>
+        <v>0.739795918367347</v>
       </c>
       <c r="B5" t="n">
-        <v>0.728050520907664</v>
+        <v>0.772098139955283</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9375</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.785714285714286</v>
+        <v>0.821428571428571</v>
       </c>
       <c r="E5" t="n">
-        <v>0.681952482870218</v>
+        <v>0.721129972047708</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
@@ -475,19 +475,19 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.556122448979592</v>
+        <v>0.566326530612245</v>
       </c>
       <c r="B6" t="n">
-        <v>0.573828948828949</v>
+        <v>0.496646409146409</v>
       </c>
       <c r="C6" t="n">
-        <v>0.625</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="D6" t="n">
-        <v>0.607142857142857</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.523752364398096</v>
+        <v>0.619047619047619</v>
+      </c>
+      <c r="E6" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F6" t="s">
         <v>10</v>
